--- a/data/final/medical_status.xlsx
+++ b/data/final/medical_status.xlsx
@@ -44,27 +44,30 @@
     <t>Bruno Fernandes</t>
   </si>
   <si>
+    <t>Moderate Risk</t>
+  </si>
+  <si>
+    <t>Bryan Mbeumo</t>
+  </si>
+  <si>
+    <t>Luke Shaw</t>
+  </si>
+  <si>
+    <t>Matthijs de Ligt</t>
+  </si>
+  <si>
+    <t>Low Risk</t>
+  </si>
+  <si>
+    <t>Amad Diallo</t>
+  </si>
+  <si>
+    <t>Diogo Dalot</t>
+  </si>
+  <si>
     <t>High Risk</t>
   </si>
   <si>
-    <t>Bryan Mbeumo</t>
-  </si>
-  <si>
-    <t>Moderate Risk</t>
-  </si>
-  <si>
-    <t>Luke Shaw</t>
-  </si>
-  <si>
-    <t>Matthijs de Ligt</t>
-  </si>
-  <si>
-    <t>Amad Diallo</t>
-  </si>
-  <si>
-    <t>Diogo Dalot</t>
-  </si>
-  <si>
     <t>Matheus Cunha</t>
   </si>
   <si>
@@ -96,9 +99,6 @@
   </si>
   <si>
     <t>Joshua Zirkzee</t>
-  </si>
-  <si>
-    <t>Low Risk</t>
   </si>
   <si>
     <t>Manuel Ugarte</t>
@@ -229,19 +229,19 @@
         <v>9</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.7605645555997812</v>
+        <v>1.8267716535433052</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.09256227143485958</v>
+        <v>1.214835164835165</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-0.9185324733722408</v>
+        <v>0.41705282669138016</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.5102671354467484</v>
+        <v>1.6799999999999988</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.5750980840824361</v>
+        <v>1.602356523273517</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>10</v>
@@ -258,22 +258,22 @@
         <v>11</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.033784557724369016</v>
+        <v>1.3307086614173236</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.7976209838252747</v>
+        <v>1.7489010989010971</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.966524088361889</v>
+        <v>1.801668211306765</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1.242958406857476</v>
+        <v>2.1600000000000006</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.2665167048589652</v>
+        <v>1.0291632003117162</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>19.0</v>
@@ -284,25 +284,25 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-0.11618591802769947</v>
+        <v>1.2283464566929154</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-1.0324851183979962</v>
+        <v>0.3626373626373639</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-1.107795180373659</v>
+        <v>0.2780352177942535</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.32709431759407115</v>
+        <v>1.5600000000000018</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.011808451315647811</v>
+        <v>1.113019411914677</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>113.0</v>
@@ -313,25 +313,25 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0.9527559055118112</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0.4994505494505505</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1.0106580166821122</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>2.4000000000000012</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.587049911475651</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>-0.5199525835140444</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>-0.8518682260263771</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>-0.11038071447618335</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>1.6093040425628395</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>-0.05101350932870519</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>31.0</v>
@@ -345,22 +345,22 @@
         <v>15</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-0.6814592497085781</v>
+        <v>0.8425196850393726</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.7671554839071727</v>
+        <v>1.7258241758241757</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1.6213730545867977</v>
+        <v>2.2826691380908244</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.5251681318262444</v>
+        <v>3.0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.1340371490266803</v>
+        <v>0.41433203872306307</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>42.0</v>
@@ -374,22 +374,22 @@
         <v>16</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2.341022646217748</v>
+        <v>2.9055118110236178</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2.214266730017134</v>
+        <v>2.8219780219780217</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.6516720565002382</v>
+        <v>0.6130676552363309</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.9551154073747066</v>
+        <v>0.7199999999999962</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1.3122359385056015</v>
+        <v>2.86304221742888</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>11.0</v>
@@ -400,25 +400,25 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.24143598568877406</v>
+        <v>1.4724409448818911</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.8215581623323602</v>
+        <v>1.7670329670329679</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.4744410501582021</v>
+        <v>1.440222428174236</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-2.0541523144907887</v>
+        <v>0.0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.21582653735563723</v>
+        <v>1.826089201177208</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>7.0</v>
@@ -429,25 +429,25 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-0.4045906790893735</v>
+        <v>1.0314960629921275</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.4449361914059821</v>
+        <v>0.8076923076923086</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.1829764813760156</v>
+        <v>1.226135310472659</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.039251318111292614</v>
+        <v>1.320000000000001</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-0.2972863454302379</v>
+        <v>0.9806530364990721</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>17.0</v>
@@ -458,22 +458,22 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.8989988409093845</v>
+        <v>1.9212598425196832</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1.3503521966251717</v>
+        <v>2.167582417582417</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.06752623010514922</v>
+        <v>1.1413345690454109</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.039251318111292614</v>
+        <v>1.320000000000001</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.6308821338312891</v>
+        <v>1.8649096642190248</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>10</v>
@@ -487,25 +487,25 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.7028836033874512</v>
+        <v>1.7874015748031504</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.6756035479287734</v>
+        <v>0.6329670329670336</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>-1.4863205943764957</v>
+        <v>0.0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.039251318111292614</v>
+        <v>1.320000000000001</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.36652222945645513</v>
+        <v>1.6130566841082952</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>2.0</v>
@@ -516,22 +516,22 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.7144197938299142</v>
+        <v>1.7952755905511797</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-0.09240683521077454</v>
+        <v>1.0747252747252747</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-0.7992969679613458</v>
+        <v>0.5046339202965711</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1.4261312247101532</v>
+        <v>2.2799999999999976</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.6720308575720761</v>
+        <v>1.3456896418504416</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>10</v>
@@ -545,25 +545,25 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-0.012360204045498044</v>
+        <v>1.299212598425198</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.6124964409555556</v>
+        <v>0.6807692307692326</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>-0.5456849405794452</v>
+        <v>0.690917516218721</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.7719425895220201</v>
+        <v>0.8399999999999994</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-0.2027017114433282</v>
+        <v>1.3499738465346836</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>0.0</v>
@@ -574,25 +574,25 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.541376937192911</v>
+        <v>1.6771653543307077</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1.069634375951208</v>
+        <v>1.9549450549450538</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.24543317468648546</v>
+        <v>1.2720111214087122</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.2224241359639791</v>
+        <v>1.1999999999999975</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.3633190598752279</v>
+        <v>1.6798078060588422</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>63.0</v>
@@ -603,25 +603,25 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.16068265259150288</v>
+        <v>1.4173228346456686</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1.2284901969527553</v>
+        <v>2.0752747252747263</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.6390996052494364</v>
+        <v>1.5611677479147366</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.7719425895220201</v>
+        <v>0.8399999999999994</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.0811530386909235</v>
+        <v>1.620399367034696</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>29.0</v>
@@ -632,25 +632,25 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.2645083665737087</v>
+        <v>1.4881889763779543</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.6668991193807431</v>
+        <v>0.6395604395604405</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>-1.2535274647647505</v>
+        <v>0.17099165894346635</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.9551154073747066</v>
+        <v>0.7199999999999962</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-0.014464440066378925</v>
+        <v>1.5991083207679786</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>28.0</v>
@@ -661,25 +661,25 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-0.19693925112496846</v>
+        <v>1.1732283464566946</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.7582956191350574</v>
+        <v>0.5703296703296706</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>-0.418878926888493</v>
+        <v>0.7840593141797974</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.2224241359639791</v>
+        <v>1.1999999999999975</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-0.2192116844926006</v>
+        <v>1.1248367172240639</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>31.0</v>
@@ -690,25 +690,25 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-1.1544430578497247</v>
+        <v>0.5196850393700795</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>-0.9541452614657273</v>
+        <v>0.4219780219780235</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1.085759593772784</v>
+        <v>1.889249304911956</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.14392149974138463</v>
+        <v>1.4399999999999982</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-0.8309590044201153</v>
+        <v>0.4024257975677498</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>20.0</v>
@@ -722,22 +722,22 @@
         <v>29</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-1.915831627052543</v>
+        <v>0.0</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-0.07499797811471387</v>
+        <v>1.0879120879120887</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2.5979686227141183</v>
+        <v>3.0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.5102671354467484</v>
+        <v>1.6799999999999988</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-1.1068308614505427</v>
+        <v>0.0</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>3.0</v>
@@ -751,22 +751,22 @@
         <v>30</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-0.5430249643989725</v>
+        <v>0.9370078740157521</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-0.7495911905870271</v>
+        <v>0.5769230769230775</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>-0.1501258829464817</v>
+        <v>0.9814643188137152</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-1.1382882252273838</v>
+        <v>0.5999999999999989</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-0.5750890036425775</v>
+        <v>1.1348097754586361</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>38.0</v>
@@ -780,22 +780,22 @@
         <v>31</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-1.339022104929195</v>
+        <v>0.3937007874015759</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.37312465588473814</v>
+        <v>0.8620879120879114</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1.0024840026921586</v>
+        <v>1.8280815569972189</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-1.1382882252273838</v>
+        <v>0.5999999999999989</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-0.9900933462803113</v>
+        <v>0.7394393780476526</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>13.0</v>
@@ -809,22 +809,22 @@
         <v>32</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-0.46227163130171006</v>
+        <v>0.9921259842519685</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.8845098330814888</v>
+        <v>0.47472527472527604</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>-0.4359125705186235</v>
+        <v>0.7715477293790537</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.9551154073747066</v>
+        <v>0.7199999999999962</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-0.4867630965971873</v>
+        <v>1.1491542158484973</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>0.0</v>
@@ -838,19 +838,19 @@
         <v>33</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.8989988409093889</v>
+        <v>1.921259842519686</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.0773295214758086</v>
+        <v>1.2032967032967041</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>-0.8371495093616279</v>
+        <v>0.4768303985171468</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.32709431759407115</v>
+        <v>1.5600000000000018</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.5668307400783781</v>
+        <v>1.6642830579886905</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>10</v>
@@ -867,22 +867,22 @@
         <v>34</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-1.3159497240442626</v>
+        <v>0.40944881889763796</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.07515341433879891</v>
+        <v>1.201648351648351</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1.6630108501271086</v>
+        <v>2.3132530120481913</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.32709431759407115</v>
+        <v>1.5600000000000018</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-0.7089773563373998</v>
+        <v>0.4488337186058182</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>100.0</v>
@@ -896,22 +896,22 @@
         <v>35</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>-1.119834486522327</v>
+        <v>0.5433070866141718</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-0.7952894404641841</v>
+        <v>0.5423076923076926</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.6769521466497186</v>
+        <v>1.5889712696941607</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-0.039251318111292614</v>
+        <v>1.320000000000001</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-0.7340051233510627</v>
+        <v>0.5645955184356546</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>18.0</v>
@@ -925,22 +925,22 @@
         <v>36</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2.479456931527356</v>
+        <v>3.0</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>2.4492863008139403</v>
+        <v>3.0</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>-0.4680872307088646</v>
+        <v>0.7479147358665422</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-1.321461043080061</v>
+        <v>0.48000000000000154</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>1.3094567387638203</v>
+        <v>3.0</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>0.0</v>
@@ -954,22 +954,22 @@
         <v>37</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-0.5430249643989791</v>
+        <v>0.9370078740157478</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>-1.5112286885396393</v>
+        <v>0.0</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>-0.9166398463022246</v>
+        <v>0.41844300278035296</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.5102671354467484</v>
+        <v>1.6799999999999988</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-0.28248451332475794</v>
+        <v>0.7853463440677512</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>70.0</v>
@@ -983,22 +983,22 @@
         <v>38</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.414478842325775</v>
+        <v>1.5905511811023612</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>-0.6951885121618395</v>
+        <v>0.6181318681318695</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>-1.0831910284634751</v>
+        <v>0.29610750695087956</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.6934399532994256</v>
+        <v>1.7999999999999967</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.32659666312614155</v>
+        <v>1.2958090094142287</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>0.0</v>
@@ -1012,22 +1012,22 @@
         <v>39</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-0.12772210847017113</v>
+        <v>1.2204724409448806</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.22965702106633107</v>
+        <v>1.3186813186813198</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>-0.04035351288565634</v>
+        <v>1.062094531974051</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.5102671354467484</v>
+        <v>1.6799999999999988</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.12283564696850383</v>
+        <v>1.171490719895928</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>0.0</v>

--- a/data/final/medical_status.xlsx
+++ b/data/final/medical_status.xlsx
@@ -229,7 +229,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.8267716535433052</v>
+        <v>1.8267716535433067</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>1.214835164835165</v>
@@ -241,7 +241,7 @@
         <v>1.6799999999999988</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1.602356523273517</v>
+        <v>1.6023565232735146</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>10</v>
@@ -258,7 +258,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.3307086614173236</v>
+        <v>1.3307086614173238</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>1.7489010989010971</v>
@@ -270,7 +270,7 @@
         <v>2.1600000000000006</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1.0291632003117162</v>
+        <v>1.0291632003117122</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>10</v>
@@ -287,7 +287,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.2283464566929154</v>
+        <v>1.228346456692914</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>0.3626373626373639</v>
@@ -299,7 +299,7 @@
         <v>1.5600000000000018</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1.113019411914677</v>
+        <v>1.1130194119146748</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>10</v>
@@ -316,7 +316,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.9527559055118112</v>
+        <v>0.9527559055118113</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>0.4994505494505505</v>
@@ -328,7 +328,7 @@
         <v>2.4000000000000012</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.587049911475651</v>
+        <v>0.5870499114756466</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>14</v>
@@ -345,7 +345,7 @@
         <v>15</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.8425196850393726</v>
+        <v>0.8425196850393728</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>1.7258241758241757</v>
@@ -357,7 +357,7 @@
         <v>3.0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.41433203872306307</v>
+        <v>0.41433203872305774</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>14</v>
@@ -374,7 +374,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2.9055118110236178</v>
+        <v>2.9055118110236213</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>2.8219780219780217</v>
@@ -386,7 +386,7 @@
         <v>0.7199999999999962</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2.86304221742888</v>
+        <v>2.8630422174288803</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>17</v>
@@ -415,7 +415,7 @@
         <v>0.0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1.826089201177208</v>
+        <v>1.8260892011772127</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>10</v>
@@ -432,7 +432,7 @@
         <v>19</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1.0314960629921275</v>
+        <v>1.0314960629921262</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>0.8076923076923086</v>
@@ -444,7 +444,7 @@
         <v>1.320000000000001</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9806530364990721</v>
+        <v>0.9806530364990708</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>14</v>
@@ -461,7 +461,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1.9212598425196832</v>
+        <v>1.9212598425196847</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>2.167582417582417</v>
@@ -473,7 +473,7 @@
         <v>1.320000000000001</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1.8649096642190248</v>
+        <v>1.864909664219025</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>10</v>
@@ -490,7 +490,7 @@
         <v>21</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1.7874015748031504</v>
+        <v>1.7874015748031509</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>0.6329670329670336</v>
@@ -502,7 +502,7 @@
         <v>1.320000000000001</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1.6130566841082952</v>
+        <v>1.613056684108293</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>10</v>
@@ -519,7 +519,7 @@
         <v>22</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1.7952755905511797</v>
+        <v>1.7952755905511812</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>1.0747252747252747</v>
@@ -531,7 +531,7 @@
         <v>2.2799999999999976</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1.3456896418504416</v>
+        <v>1.3456896418504367</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>10</v>
@@ -548,7 +548,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1.299212598425198</v>
+        <v>1.2992125984251968</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>0.6807692307692326</v>
@@ -577,7 +577,7 @@
         <v>24</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1.6771653543307077</v>
+        <v>1.6771653543307092</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>1.9549450549450538</v>
@@ -589,7 +589,7 @@
         <v>1.1999999999999975</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1.6798078060588422</v>
+        <v>1.6798078060588428</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>10</v>
@@ -618,7 +618,7 @@
         <v>0.8399999999999994</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1.620399367034696</v>
+        <v>1.6203993670346981</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>10</v>
@@ -635,7 +635,7 @@
         <v>26</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1.4881889763779543</v>
+        <v>1.4881889763779546</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>0.6395604395604405</v>
@@ -647,7 +647,7 @@
         <v>0.7199999999999962</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1.5991083207679786</v>
+        <v>1.5991083207679804</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>10</v>
@@ -664,7 +664,7 @@
         <v>27</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1.1732283464566946</v>
+        <v>1.1732283464566933</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>0.5703296703296706</v>
@@ -676,7 +676,7 @@
         <v>1.1999999999999975</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1.1248367172240639</v>
+        <v>1.1248367172240628</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>10</v>
@@ -693,7 +693,7 @@
         <v>28</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.5196850393700795</v>
+        <v>0.5196850393700783</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>0.4219780219780235</v>
@@ -705,7 +705,7 @@
         <v>1.4399999999999982</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.4024257975677498</v>
+        <v>0.40242579756774766</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>14</v>
@@ -751,7 +751,7 @@
         <v>30</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.9370078740157521</v>
+        <v>0.9370078740157493</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>0.5769230769230775</v>
@@ -763,7 +763,7 @@
         <v>0.5999999999999989</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1.1348097754586361</v>
+        <v>1.134809775458637</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>31</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.3937007874015759</v>
+        <v>0.393700787401576</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>0.8620879120879114</v>
@@ -792,7 +792,7 @@
         <v>0.5999999999999989</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.7394393780476526</v>
+        <v>0.7394393780476567</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>14</v>
@@ -809,7 +809,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.9921259842519685</v>
+        <v>0.9921259842519687</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>0.47472527472527604</v>
@@ -821,7 +821,7 @@
         <v>0.7199999999999962</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1.1491542158484973</v>
+        <v>1.1491542158484993</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>10</v>
@@ -838,7 +838,7 @@
         <v>33</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1.921259842519686</v>
+        <v>1.9212598425196834</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>1.2032967032967041</v>
@@ -850,7 +850,7 @@
         <v>1.5600000000000018</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1.6642830579886905</v>
+        <v>1.664283057988686</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>10</v>
@@ -867,7 +867,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.40944881889763796</v>
+        <v>0.4094488188976365</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>1.201648351648351</v>
@@ -879,7 +879,7 @@
         <v>1.5600000000000018</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.4488337186058182</v>
+        <v>0.4488337186058181</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>14</v>
@@ -896,7 +896,7 @@
         <v>35</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.5433070866141718</v>
+        <v>0.5433070866141749</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>0.5423076923076926</v>
@@ -908,7 +908,7 @@
         <v>1.320000000000001</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.5645955184356546</v>
+        <v>0.5645955184356564</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>14</v>
@@ -954,7 +954,7 @@
         <v>37</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.9370078740157478</v>
+        <v>0.9370078740157465</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>0.0</v>
@@ -966,7 +966,7 @@
         <v>1.6799999999999988</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.7853463440677512</v>
+        <v>0.7853463440677486</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>14</v>
@@ -983,7 +983,7 @@
         <v>38</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1.5905511811023612</v>
+        <v>1.5905511811023634</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>0.6181318681318695</v>
@@ -995,7 +995,7 @@
         <v>1.7999999999999967</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1.2958090094142287</v>
+        <v>1.295809009414226</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>10</v>
@@ -1012,7 +1012,7 @@
         <v>39</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1.2204724409448806</v>
+        <v>1.2204724409448822</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>1.3186813186813198</v>
@@ -1024,7 +1024,7 @@
         <v>1.6799999999999988</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>1.171490719895928</v>
+        <v>1.1714907198959281</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>10</v>
